--- a/wiki/reports/daily/2026-10-20_일일보고.xlsx
+++ b/wiki/reports/daily/2026-10-20_일일보고.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="165" formatCode="+0.0%;-0.0%;&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -74,11 +74,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <color rgb="00888888"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="10">
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -205,7 +200,13 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -213,6 +214,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -596,14 +606,14 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>재연마 일일생산 보고  ─  2026년 10월 20일  (2026-10-20 08:05 생성 · 속보값)</t>
+          <t>재연마 일일생산 보고  ─  2026년 10월 20일  (2026-10-20 16:00 생성 · 속보값)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>생성: 2026-10-20 08:05   |   전일: 10월 19일   |   월평균 기준: 이전 작업일 11일 평균   |   10월 누적 작업일: 11일</t>
+          <t>생성: 2026-10-20 16:00   |   전일: 10월 19일   |   월평균 기준: 이전 작업일 11일 평균   |   10월 누적 작업일: 12일</t>
         </is>
       </c>
     </row>
@@ -665,25 +675,25 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>50</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>-50</v>
+        <v>-30</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>-1</v>
+        <v>-0.6</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>46</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>-46</v>
+        <v>-26</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>-1</v>
+        <v>-0.5652173913043478</v>
       </c>
       <c r="I4" s="10" t="inlineStr"/>
     </row>
@@ -694,29 +704,29 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0</v>
+        <v>5820</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>9666</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>-9666</v>
+        <v>-3846</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>-1</v>
+        <v>-0.3978895096213532</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>10371.7</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>-10371.72727272727</v>
+        <v>-4551.727272727272</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>-1</v>
+        <v>-0.4388591362883363</v>
       </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
-          <t>0:00:00</t>
+          <t>1:37:00</t>
         </is>
       </c>
     </row>
@@ -727,25 +737,25 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>25</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>-25</v>
+        <v>-21</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>-1</v>
+        <v>-0.84</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>30.2</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>-30.18181818181818</v>
+        <v>-26.18181818181818</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>-1</v>
+        <v>-0.8674698795180723</v>
       </c>
       <c r="I6" s="10" t="inlineStr"/>
     </row>
@@ -756,29 +766,29 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>6706</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>-6706</v>
+        <v>-5726</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>-1</v>
+        <v>-0.8538622129436325</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>9804.5</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>-9804.545454545454</v>
+        <v>-8824.545454545454</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>-1</v>
+        <v>-0.9000463606861382</v>
       </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
-          <t>0:00:00</t>
+          <t>0:16:20</t>
         </is>
       </c>
     </row>
@@ -789,25 +799,25 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>75</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>-75</v>
+        <v>-51</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>-1</v>
+        <v>-0.68</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>76.2</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>-76.18181818181819</v>
+        <v>-52.18181818181819</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>-1</v>
+        <v>-0.684964200477327</v>
       </c>
       <c r="I8" s="10" t="inlineStr"/>
     </row>
@@ -818,29 +828,29 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>0</v>
+        <v>6800</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>16372</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>-16372</v>
+        <v>-9572</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>-1</v>
+        <v>-0.5846567310041534</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>20176.3</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>-20176.27272727273</v>
+        <v>-13376.27272727273</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>-1</v>
+        <v>-0.6629704558459757</v>
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
-          <t>0:00:00</t>
+          <t>1:53:20</t>
         </is>
       </c>
     </row>
@@ -851,43 +861,43 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>75</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>-75</v>
+        <v>-51</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>-1</v>
+        <v>-0.68</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>76.2</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>-76.18181818181819</v>
+        <v>-52.18181818181819</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>-1</v>
+        <v>-0.684964200477327</v>
       </c>
       <c r="I10" s="10" t="inlineStr"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>10월 누적  (11일 / 20일 중 작업일)</t>
+          <t>10월 누적  (12일 / 20일 중 작업일)</t>
         </is>
       </c>
       <c r="B11" s="13" t="n"/>
       <c r="C11" s="14" t="n">
-        <v>838</v>
+        <v>862</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>221939</v>
+        <v>228739</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>838</v>
+        <v>862</v>
       </c>
       <c r="F11" s="13" t="n"/>
       <c r="G11" s="13" t="n"/>
@@ -910,7 +920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -997,90 +1007,290 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="17" t="inlineStr">
-        <is>
-          <t>(해당일 작업 없음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="inlineStr">
+        <is>
+          <t>0040, 0088</t>
+        </is>
+      </c>
+      <c r="H4" s="17" t="inlineStr"/>
+      <c r="I4" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="J4" s="19" t="n">
+        <v>1530</v>
+      </c>
+      <c r="K4" s="17" t="inlineStr">
+        <is>
+          <t>0:25:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>면취</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G5" s="18" t="inlineStr">
+        <is>
+          <t>0030</t>
+        </is>
+      </c>
+      <c r="H5" s="17" t="inlineStr"/>
+      <c r="I5" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="J5" s="19" t="n">
+        <v>4290</v>
+      </c>
+      <c r="K5" s="17" t="inlineStr">
+        <is>
+          <t>1:11:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>FAST GRIND 소계</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="n"/>
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="13" t="n"/>
+      <c r="G6" s="13" t="n"/>
+      <c r="H6" s="13" t="n"/>
+      <c r="I6" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="J6" s="14" t="n">
+        <v>5820</v>
+      </c>
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>1:37:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>■ GX7</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>순서</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>형상</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>날수(F)</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>날경(Ø)</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>상크경(Ø)</t>
         </is>
       </c>
-      <c r="F7" s="19" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>코팅</t>
         </is>
       </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>특이사항</t>
         </is>
       </c>
-      <c r="H7" s="19" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I7" s="19" t="inlineStr">
+      <c r="I9" s="21" t="inlineStr">
         <is>
           <t>수량(개)</t>
         </is>
       </c>
-      <c r="J7" s="19" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t>시간합계(초)</t>
         </is>
       </c>
-      <c r="K7" s="19" t="inlineStr">
+      <c r="K9" s="21" t="inlineStr">
         <is>
           <t>시간(H:M:S)</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="17" t="inlineStr">
-        <is>
-          <t>(해당일 작업 없음)</t>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>드릴</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="E10" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t>0175</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr"/>
+      <c r="I10" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" s="24" t="n">
+        <v>530</v>
+      </c>
+      <c r="K10" s="22" t="inlineStr">
+        <is>
+          <t>0:08:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>드릴</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="E11" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>틴</t>
+        </is>
+      </c>
+      <c r="G11" s="23" t="inlineStr">
+        <is>
+          <t>0175</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr"/>
+      <c r="I11" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" s="24" t="n">
+        <v>450</v>
+      </c>
+      <c r="K11" s="22" t="inlineStr">
+        <is>
+          <t>0:07:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>GX7 소계</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="n"/>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="13" t="n"/>
+      <c r="H12" s="13" t="n"/>
+      <c r="I12" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>980</v>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>0:16:20</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A6:K6"/>
-    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A12:H12"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A6:H6"/>
     <mergeCell ref="A8:K8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
